--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/6.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/6.xlsx
@@ -426,13 +426,13 @@
         <v>-0.2748769927316904</v>
       </c>
       <c r="E2">
-        <v>-12.57054816445539</v>
+        <v>-12.43006579139307</v>
       </c>
       <c r="F2">
-        <v>-5.129773805213213</v>
+        <v>-5.792686416447157</v>
       </c>
       <c r="G2">
-        <v>-9.355404281496453</v>
+        <v>-3.481295525478633</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.11102257943081</v>
       </c>
       <c r="E3">
-        <v>-13.56904661832537</v>
+        <v>-13.47056151817971</v>
       </c>
       <c r="F3">
-        <v>-5.007116615513287</v>
+        <v>-5.969350675707402</v>
       </c>
       <c r="G3">
-        <v>-9.082713314326964</v>
+        <v>-3.657933283024176</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.939607752935514</v>
       </c>
       <c r="E4">
-        <v>-13.7633919890594</v>
+        <v>-13.42417845410403</v>
       </c>
       <c r="F4">
-        <v>-5.067499628972954</v>
+        <v>-6.215397331891327</v>
       </c>
       <c r="G4">
-        <v>-9.158569803794057</v>
+        <v>-3.612850945424831</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.643575464153476</v>
       </c>
       <c r="E5">
-        <v>-13.96099763068342</v>
+        <v>-13.13354087880385</v>
       </c>
       <c r="F5">
-        <v>-4.945815770971318</v>
+        <v>-6.046468367438425</v>
       </c>
       <c r="G5">
-        <v>-8.554922577042912</v>
+        <v>-3.656257184996681</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.209650987622027</v>
       </c>
       <c r="E6">
-        <v>-15.34255922467631</v>
+        <v>-13.45662334097359</v>
       </c>
       <c r="F6">
-        <v>-4.57482563105574</v>
+        <v>-5.958339187821988</v>
       </c>
       <c r="G6">
-        <v>-8.329495224578645</v>
+        <v>-4.180465980701726</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.598416764488219</v>
       </c>
       <c r="E7">
-        <v>-15.44599910593248</v>
+        <v>-15.11844363516591</v>
       </c>
       <c r="F7">
-        <v>-4.791876114672072</v>
+        <v>-5.884877081439519</v>
       </c>
       <c r="G7">
-        <v>-9.682449645680622</v>
+        <v>-3.9091965639621</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.798579491351479</v>
       </c>
       <c r="E8">
-        <v>-16.92566370462915</v>
+        <v>-15.66346955732316</v>
       </c>
       <c r="F8">
-        <v>-4.997702219980471</v>
+        <v>-6.017465567931608</v>
       </c>
       <c r="G8">
-        <v>-9.430160342118389</v>
+        <v>-4.141341362259302</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.798706932713091</v>
       </c>
       <c r="E9">
-        <v>-16.92086674554897</v>
+        <v>-15.44892296670516</v>
       </c>
       <c r="F9">
-        <v>-5.059722915795473</v>
+        <v>-5.920163876063972</v>
       </c>
       <c r="G9">
-        <v>-9.330016095720172</v>
+        <v>-3.933706234183472</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.609951395103833</v>
       </c>
       <c r="E10">
-        <v>-16.08272793414195</v>
+        <v>-16.84894558503692</v>
       </c>
       <c r="F10">
-        <v>-4.210932114679945</v>
+        <v>-5.806734699231233</v>
       </c>
       <c r="G10">
-        <v>-8.784074156666403</v>
+        <v>-3.845301200839194</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.254785452639048</v>
       </c>
       <c r="E11">
-        <v>-17.90190094579805</v>
+        <v>-17.42308136536989</v>
       </c>
       <c r="F11">
-        <v>-4.279320470720267</v>
+        <v>-5.751619274085968</v>
       </c>
       <c r="G11">
-        <v>-8.063511260263727</v>
+        <v>-3.625622707964558</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.774474635896143</v>
       </c>
       <c r="E12">
-        <v>-17.27670143222631</v>
+        <v>-17.87222209767082</v>
       </c>
       <c r="F12">
-        <v>-3.919180287046557</v>
+        <v>-5.866290173655504</v>
       </c>
       <c r="G12">
-        <v>-7.399190329215109</v>
+        <v>-3.141110283767389</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.218205541474109</v>
       </c>
       <c r="E13">
-        <v>-19.25085567767971</v>
+        <v>-18.19844023439081</v>
       </c>
       <c r="F13">
-        <v>-3.896872352889166</v>
+        <v>-5.528940862335016</v>
       </c>
       <c r="G13">
-        <v>-6.73522837554777</v>
+        <v>-3.119566419401523</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.642445368606294</v>
       </c>
       <c r="E14">
-        <v>-19.85454155658883</v>
+        <v>-19.60029026570548</v>
       </c>
       <c r="F14">
-        <v>-4.235754972272235</v>
+        <v>-5.371618153562737</v>
       </c>
       <c r="G14">
-        <v>-7.437936389691822</v>
+        <v>-2.280950874077886</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.100096995603037</v>
       </c>
       <c r="E15">
-        <v>-22.21005197231064</v>
+        <v>-20.71325953011038</v>
       </c>
       <c r="F15">
-        <v>-3.31608242923396</v>
+        <v>-4.894539000370626</v>
       </c>
       <c r="G15">
-        <v>-6.268108731816598</v>
+        <v>-2.230184945503689</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6356677157096231</v>
       </c>
       <c r="E16">
-        <v>-20.84325919778884</v>
+        <v>-22.43253534977038</v>
       </c>
       <c r="F16">
-        <v>-2.943380053896795</v>
+        <v>-4.633616522367227</v>
       </c>
       <c r="G16">
-        <v>-6.506443605539331</v>
+        <v>-2.010908507296084</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.2848498416219068</v>
       </c>
       <c r="E17">
-        <v>-22.52364849981447</v>
+        <v>-22.695612214719</v>
       </c>
       <c r="F17">
-        <v>-3.027303612209219</v>
+        <v>-4.283690937137437</v>
       </c>
       <c r="G17">
-        <v>-5.866894724543491</v>
+        <v>-1.5423529540398</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.06359239248475666</v>
       </c>
       <c r="E18">
-        <v>-23.21881301136427</v>
+        <v>-23.29099582418979</v>
       </c>
       <c r="F18">
-        <v>-3.176112360815524</v>
+        <v>-3.97459392445683</v>
       </c>
       <c r="G18">
-        <v>-6.321195612332296</v>
+        <v>-1.404317666018458</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.0237013924605123</v>
       </c>
       <c r="E19">
-        <v>-24.86871358905433</v>
+        <v>-24.50295688052199</v>
       </c>
       <c r="F19">
-        <v>-2.530176311134554</v>
+        <v>-3.651048527536593</v>
       </c>
       <c r="G19">
-        <v>-5.361130839374661</v>
+        <v>-1.361488401001245</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.01657864393013995</v>
       </c>
       <c r="E20">
-        <v>-23.62487248259276</v>
+        <v>-24.56643456241066</v>
       </c>
       <c r="F20">
-        <v>-2.135258778789112</v>
+        <v>-3.33857674605698</v>
       </c>
       <c r="G20">
-        <v>-6.009399607304819</v>
+        <v>-1.394618749862472</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.1622610316255579</v>
       </c>
       <c r="E21">
-        <v>-25.93136669825894</v>
+        <v>-26.25130933266711</v>
       </c>
       <c r="F21">
-        <v>-1.831515504632798</v>
+        <v>-3.265595921135538</v>
       </c>
       <c r="G21">
-        <v>-5.699107391161823</v>
+        <v>-1.008440020689586</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.392775486777685</v>
       </c>
       <c r="E22">
-        <v>-25.30758342974897</v>
+        <v>-26.71553868171114</v>
       </c>
       <c r="F22">
-        <v>-2.153934321885227</v>
+        <v>-2.985157935489585</v>
       </c>
       <c r="G22">
-        <v>-5.175734033725933</v>
+        <v>-1.357632331240171</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6834517265089528</v>
       </c>
       <c r="E23">
-        <v>-26.82361354680583</v>
+        <v>-26.22494890038842</v>
       </c>
       <c r="F23">
-        <v>-0.9156501381777888</v>
+        <v>-2.741398401704789</v>
       </c>
       <c r="G23">
-        <v>-5.444311772792121</v>
+        <v>-1.554278835332005</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.00595605940695</v>
       </c>
       <c r="E24">
-        <v>-27.76694489464811</v>
+        <v>-27.33305890754327</v>
       </c>
       <c r="F24">
-        <v>-1.224753777797619</v>
+        <v>-2.440005205870217</v>
       </c>
       <c r="G24">
-        <v>-5.275346993599861</v>
+        <v>-1.635269354037522</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.339843906417845</v>
       </c>
       <c r="E25">
-        <v>-27.83406494286866</v>
+        <v>-27.60339558588769</v>
       </c>
       <c r="F25">
-        <v>-0.6432630553196442</v>
+        <v>-2.611515363150243</v>
       </c>
       <c r="G25">
-        <v>-5.709064771032328</v>
+        <v>-1.374127015566824</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.663775897302058</v>
       </c>
       <c r="E26">
-        <v>-28.90895548924188</v>
+        <v>-27.36127997849548</v>
       </c>
       <c r="F26">
-        <v>-0.9920595757794181</v>
+        <v>-2.603387422193975</v>
       </c>
       <c r="G26">
-        <v>-5.846640568005634</v>
+        <v>-1.530842181137581</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.958214738331123</v>
       </c>
       <c r="E27">
-        <v>-25.71431156800075</v>
+        <v>-27.49019565801816</v>
       </c>
       <c r="F27">
-        <v>-0.70138793923928</v>
+        <v>-2.498368659601859</v>
       </c>
       <c r="G27">
-        <v>-6.380762360923137</v>
+        <v>-1.334501134162907</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.20972524421271</v>
       </c>
       <c r="E28">
-        <v>-27.87444661657997</v>
+        <v>-27.03222104522932</v>
       </c>
       <c r="F28">
-        <v>-0.9785853516054813</v>
+        <v>-2.563675488903766</v>
       </c>
       <c r="G28">
-        <v>-5.859232189168574</v>
+        <v>-2.028849544126214</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.406055411107575</v>
       </c>
       <c r="E29">
-        <v>-27.65447593197175</v>
+        <v>-28.70881846531538</v>
       </c>
       <c r="F29">
-        <v>-0.5100309273555802</v>
+        <v>-2.718212398100431</v>
       </c>
       <c r="G29">
-        <v>-5.405905109112254</v>
+        <v>-2.35417181688025</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.539386107250472</v>
       </c>
       <c r="E30">
-        <v>-27.82080789231981</v>
+        <v>-27.20542241710864</v>
       </c>
       <c r="F30">
-        <v>-1.48140685020699</v>
+        <v>-2.895276758816228</v>
       </c>
       <c r="G30">
-        <v>-6.22920602666442</v>
+        <v>-1.555142991791664</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.606272832685318</v>
       </c>
       <c r="E31">
-        <v>-26.19532819721974</v>
+        <v>-26.86939024202809</v>
       </c>
       <c r="F31">
-        <v>-0.8626644456251213</v>
+        <v>-2.925940434965657</v>
       </c>
       <c r="G31">
-        <v>-5.13867451425508</v>
+        <v>-1.09978997393264</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.605475205243482</v>
       </c>
       <c r="E32">
-        <v>-28.26139923910858</v>
+        <v>-26.61079469209896</v>
       </c>
       <c r="F32">
-        <v>-1.053162440512118</v>
+        <v>-3.171483443768681</v>
       </c>
       <c r="G32">
-        <v>-5.89078825904136</v>
+        <v>-1.311544856973248</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.538630122502569</v>
       </c>
       <c r="E33">
-        <v>-26.90190158027885</v>
+        <v>-26.02711898535286</v>
       </c>
       <c r="F33">
-        <v>-1.941521867357169</v>
+        <v>-3.218188454673323</v>
       </c>
       <c r="G33">
-        <v>-4.704489413540803</v>
+        <v>-0.9010339882111859</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.409977032255929</v>
       </c>
       <c r="E34">
-        <v>-26.24604721391855</v>
+        <v>-25.65654039847238</v>
       </c>
       <c r="F34">
-        <v>-0.9334592089705754</v>
+        <v>-3.153475564799222</v>
       </c>
       <c r="G34">
-        <v>-4.73504034674601</v>
+        <v>-0.2720481798309908</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.225228027504221</v>
       </c>
       <c r="E35">
-        <v>-26.0371946760269</v>
+        <v>-26.16256351307817</v>
       </c>
       <c r="F35">
-        <v>-1.63213741118779</v>
+        <v>-3.213300258629403</v>
       </c>
       <c r="G35">
-        <v>-3.861934254629177</v>
+        <v>-0.5906869464317762</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.993365595845464</v>
       </c>
       <c r="E36">
-        <v>-25.82707956189249</v>
+        <v>-25.49594817617524</v>
       </c>
       <c r="F36">
-        <v>-1.387534599386944</v>
+        <v>-3.002806303006229</v>
       </c>
       <c r="G36">
-        <v>-4.541764313921303</v>
+        <v>-0.2255482079186721</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.725645983535579</v>
       </c>
       <c r="E37">
-        <v>-24.95718944990715</v>
+        <v>-23.98607311830177</v>
       </c>
       <c r="F37">
-        <v>-1.056642411971279</v>
+        <v>-3.172957109378261</v>
       </c>
       <c r="G37">
-        <v>-3.924054311430126</v>
+        <v>0.2258364781618595</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.433909978879486</v>
       </c>
       <c r="E38">
-        <v>-24.62524818798156</v>
+        <v>-23.85807529848188</v>
       </c>
       <c r="F38">
-        <v>-1.342254380415117</v>
+        <v>-3.030327153229437</v>
       </c>
       <c r="G38">
-        <v>-3.117704958508059</v>
+        <v>0.5469528413796114</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.134472000866085</v>
       </c>
       <c r="E39">
-        <v>-25.46366111133602</v>
+        <v>-23.96843858301655</v>
       </c>
       <c r="F39">
-        <v>-1.733064867177479</v>
+        <v>-3.063634978128602</v>
       </c>
       <c r="G39">
-        <v>-3.207728653498827</v>
+        <v>0.6844607589935482</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8435887282089358</v>
       </c>
       <c r="E40">
-        <v>-25.65923998583352</v>
+        <v>-23.21138706951548</v>
       </c>
       <c r="F40">
-        <v>-1.233097094278615</v>
+        <v>-2.620295229252515</v>
       </c>
       <c r="G40">
-        <v>-3.588477033922198</v>
+        <v>1.112267810671736</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.5755859981728713</v>
       </c>
       <c r="E41">
-        <v>-21.69071366219746</v>
+        <v>-22.94857601009165</v>
       </c>
       <c r="F41">
-        <v>-1.055565534347639</v>
+        <v>-2.624624277299545</v>
       </c>
       <c r="G41">
-        <v>-2.98471885052593</v>
+        <v>0.9106504488784211</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3483443186666962</v>
       </c>
       <c r="E42">
-        <v>-24.16558321818351</v>
+        <v>-22.41323537674391</v>
       </c>
       <c r="F42">
-        <v>-0.8703980836976575</v>
+        <v>-2.689833359247922</v>
       </c>
       <c r="G42">
-        <v>-2.540610309620832</v>
+        <v>1.165991712867665</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.173617196428937</v>
       </c>
       <c r="E43">
-        <v>-22.05351328426653</v>
+        <v>-22.13077547454231</v>
       </c>
       <c r="F43">
-        <v>-1.319387298260837</v>
+        <v>-2.756958454998975</v>
       </c>
       <c r="G43">
-        <v>-3.433242160534602</v>
+        <v>1.258553051600995</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.05952223800881944</v>
       </c>
       <c r="E44">
-        <v>-21.66530016210083</v>
+        <v>-22.41117953713811</v>
       </c>
       <c r="F44">
-        <v>-0.7230232390655974</v>
+        <v>-2.258047678906083</v>
       </c>
       <c r="G44">
-        <v>-3.067314977154981</v>
+        <v>1.44861003634486</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.01485771890404735</v>
       </c>
       <c r="E45">
-        <v>-21.59045098760477</v>
+        <v>-21.69999193629712</v>
       </c>
       <c r="F45">
-        <v>-1.397844460082187</v>
+        <v>-2.757650970147715</v>
       </c>
       <c r="G45">
-        <v>-3.575744432551338</v>
+        <v>1.914591395434306</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.03988231991971029</v>
       </c>
       <c r="E46">
-        <v>-22.10372976239503</v>
+        <v>-21.07574350811877</v>
       </c>
       <c r="F46">
-        <v>-1.266744549812929</v>
+        <v>-2.486458393084408</v>
       </c>
       <c r="G46">
-        <v>-2.530337029654801</v>
+        <v>1.731920207138701</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1336897402669426</v>
       </c>
       <c r="E47">
-        <v>-21.6030850564549</v>
+        <v>-20.53080895661067</v>
       </c>
       <c r="F47">
-        <v>-1.606534231502063</v>
+        <v>-2.412828128119171</v>
       </c>
       <c r="G47">
-        <v>-2.669949207409175</v>
+        <v>1.834109971924057</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2942550275030844</v>
       </c>
       <c r="E48">
-        <v>-19.42623333229324</v>
+        <v>-20.59122156854162</v>
       </c>
       <c r="F48">
-        <v>-0.817519250539951</v>
+        <v>-2.734153500399904</v>
       </c>
       <c r="G48">
-        <v>-2.928574788094039</v>
+        <v>1.876685994715932</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5114765359983321</v>
       </c>
       <c r="E49">
-        <v>-20.02535067874506</v>
+        <v>-19.93826199047473</v>
       </c>
       <c r="F49">
-        <v>-0.9826277845311429</v>
+        <v>-2.400719053425048</v>
       </c>
       <c r="G49">
-        <v>-2.439749413832352</v>
+        <v>1.791802855825066</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7775318774794071</v>
       </c>
       <c r="E50">
-        <v>-18.5565259616062</v>
+        <v>-19.29910768685157</v>
       </c>
       <c r="F50">
-        <v>-1.497165711677847</v>
+        <v>-2.533916389958194</v>
       </c>
       <c r="G50">
-        <v>-2.230532174534307</v>
+        <v>1.45224419281569</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.081628267284153</v>
       </c>
       <c r="E51">
-        <v>-18.9821595178086</v>
+        <v>-19.10145220669165</v>
       </c>
       <c r="F51">
-        <v>-1.693202999387365</v>
+        <v>-2.574830284349864</v>
       </c>
       <c r="G51">
-        <v>-3.205363318899279</v>
+        <v>1.678982139064697</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.407444329032421</v>
       </c>
       <c r="E52">
-        <v>-19.06773228394537</v>
+        <v>-18.67968529023266</v>
       </c>
       <c r="F52">
-        <v>-0.4439272086121796</v>
+        <v>-2.343139235256454</v>
       </c>
       <c r="G52">
-        <v>-3.174694902187471</v>
+        <v>1.445563297407031</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.743973869036778</v>
       </c>
       <c r="E53">
-        <v>-18.76026589635699</v>
+        <v>-16.84485051867064</v>
       </c>
       <c r="F53">
-        <v>-0.9852769034852957</v>
+        <v>-2.339360223164882</v>
       </c>
       <c r="G53">
-        <v>-2.627409735041575</v>
+        <v>1.413372816598604</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.077954589170122</v>
       </c>
       <c r="E54">
-        <v>-18.38239842360144</v>
+        <v>-17.41831763198031</v>
       </c>
       <c r="F54">
-        <v>-0.9692504793433336</v>
+        <v>-2.479494308329072</v>
       </c>
       <c r="G54">
-        <v>-3.172849105761554</v>
+        <v>0.6731014092776143</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.394791569753061</v>
       </c>
       <c r="E55">
-        <v>-16.93869648176646</v>
+        <v>-17.17911342572681</v>
       </c>
       <c r="F55">
-        <v>-1.207647162562406</v>
+        <v>-2.522445986531629</v>
       </c>
       <c r="G55">
-        <v>-2.971041159613088</v>
+        <v>0.6670235958695026</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.685086809713555</v>
       </c>
       <c r="E56">
-        <v>-17.54910640981049</v>
+        <v>-16.87771903309533</v>
       </c>
       <c r="F56">
-        <v>-1.821816979080821</v>
+        <v>-2.530756996683917</v>
       </c>
       <c r="G56">
-        <v>-3.673451548873753</v>
+        <v>1.070349695516821</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.938154518140009</v>
       </c>
       <c r="E57">
-        <v>-17.07634636470525</v>
+        <v>-16.40500052010334</v>
       </c>
       <c r="F57">
-        <v>-0.9719459868720433</v>
+        <v>-2.263289587830998</v>
       </c>
       <c r="G57">
-        <v>-2.861747558795313</v>
+        <v>0.5689561967935142</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.145613587988126</v>
       </c>
       <c r="E58">
-        <v>-17.64294406648366</v>
+        <v>-16.7657733750459</v>
       </c>
       <c r="F58">
-        <v>-1.619211566234507</v>
+        <v>-1.977030664445573</v>
       </c>
       <c r="G58">
-        <v>-3.4902947620842</v>
+        <v>0.7880655473472877</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.305774634982672</v>
       </c>
       <c r="E59">
-        <v>-16.25376963613236</v>
+        <v>-15.38910841720498</v>
       </c>
       <c r="F59">
-        <v>-1.37000137493929</v>
+        <v>-2.223719305366668</v>
       </c>
       <c r="G59">
-        <v>-3.525644243847874</v>
+        <v>0.4417711632928393</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.41742674744973</v>
       </c>
       <c r="E60">
-        <v>-16.32055742744693</v>
+        <v>-15.64391623840586</v>
       </c>
       <c r="F60">
-        <v>-1.930720784792067</v>
+        <v>-2.077879425531996</v>
       </c>
       <c r="G60">
-        <v>-3.069648982819436</v>
+        <v>0.5509133409243302</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.484797963435804</v>
       </c>
       <c r="E61">
-        <v>-15.75168376586251</v>
+        <v>-15.46414863942199</v>
       </c>
       <c r="F61">
-        <v>-1.532515462224914</v>
+        <v>-2.615282778098175</v>
       </c>
       <c r="G61">
-        <v>-4.181183935464283</v>
+        <v>0.5736033221656958</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.516795680143375</v>
       </c>
       <c r="E62">
-        <v>-15.28460531384965</v>
+        <v>-15.42088879026257</v>
       </c>
       <c r="F62">
-        <v>-1.091027942861486</v>
+        <v>-2.565141699206721</v>
       </c>
       <c r="G62">
-        <v>-4.385845425450835</v>
+        <v>0.032771915649032</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.518931415003435</v>
       </c>
       <c r="E63">
-        <v>-14.53912880031087</v>
+        <v>-14.39648260414831</v>
       </c>
       <c r="F63">
-        <v>-1.245503552870344</v>
+        <v>-2.396749516830832</v>
       </c>
       <c r="G63">
-        <v>-3.655789861714871</v>
+        <v>-0.3715436561983181</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.501871844742347</v>
       </c>
       <c r="E64">
-        <v>-15.18459183193645</v>
+        <v>-14.75966847487059</v>
       </c>
       <c r="F64">
-        <v>-1.819230816049281</v>
+        <v>-2.394440028511827</v>
       </c>
       <c r="G64">
-        <v>-4.813939659034045</v>
+        <v>-0.6189430351413953</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.475622876898441</v>
       </c>
       <c r="E65">
-        <v>-15.04763138207758</v>
+        <v>-14.15055850197124</v>
       </c>
       <c r="F65">
-        <v>-1.716683901787119</v>
+        <v>-2.4008234277178</v>
       </c>
       <c r="G65">
-        <v>-4.569519139669429</v>
+        <v>-0.347550913405987</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.443302758189046</v>
       </c>
       <c r="E66">
-        <v>-15.11291571089256</v>
+        <v>-13.84632331279357</v>
       </c>
       <c r="F66">
-        <v>-1.664566338272585</v>
+        <v>-2.279412102591685</v>
       </c>
       <c r="G66">
-        <v>-5.328540914643794</v>
+        <v>-0.0979637304955569</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.413433767374244</v>
       </c>
       <c r="E67">
-        <v>-13.95620482481456</v>
+        <v>-14.14016301402519</v>
       </c>
       <c r="F67">
-        <v>-2.039010770257838</v>
+        <v>-2.599200853340226</v>
       </c>
       <c r="G67">
-        <v>-4.088202266851783</v>
+        <v>-0.6978266829618832</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.389024297105693</v>
       </c>
       <c r="E68">
-        <v>-14.2302918529853</v>
+        <v>-14.01993169938273</v>
       </c>
       <c r="F68">
-        <v>-1.227981097198926</v>
+        <v>-2.499780197656229</v>
       </c>
       <c r="G68">
-        <v>-4.494726528623215</v>
+        <v>-0.5132783693052673</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.366384228184154</v>
       </c>
       <c r="E69">
-        <v>-14.95500646311126</v>
+        <v>-13.24623411489175</v>
       </c>
       <c r="F69">
-        <v>-2.03493685937087</v>
+        <v>-2.823111047419141</v>
       </c>
       <c r="G69">
-        <v>-5.165241451214249</v>
+        <v>-0.3199579538225107</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.347395183751956</v>
       </c>
       <c r="E70">
-        <v>-14.88584718813021</v>
+        <v>-13.24480956340733</v>
       </c>
       <c r="F70">
-        <v>-1.958424704211293</v>
+        <v>-2.686952297420986</v>
       </c>
       <c r="G70">
-        <v>-5.646887277850374</v>
+        <v>-0.4635358526107858</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.327212959265857</v>
       </c>
       <c r="E71">
-        <v>-14.17471773224777</v>
+        <v>-14.02886525694244</v>
       </c>
       <c r="F71">
-        <v>-2.316622366325439</v>
+        <v>-2.947405091106998</v>
       </c>
       <c r="G71">
-        <v>-5.09034441038439</v>
+        <v>-0.1570344376140861</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.299469401781652</v>
       </c>
       <c r="E72">
-        <v>-13.73151609214134</v>
+        <v>-12.99933400805334</v>
       </c>
       <c r="F72">
-        <v>-1.730569824560247</v>
+        <v>-2.916584025151037</v>
       </c>
       <c r="G72">
-        <v>-4.746572005604958</v>
+        <v>-0.2907802722722286</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.264971281779615</v>
       </c>
       <c r="E73">
-        <v>-13.02566536785275</v>
+        <v>-13.34689965098294</v>
       </c>
       <c r="F73">
-        <v>-2.121599828684351</v>
+        <v>-2.886742917832587</v>
       </c>
       <c r="G73">
-        <v>-3.486926901561664</v>
+        <v>-0.5453931385205518</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.218739861119592</v>
       </c>
       <c r="E74">
-        <v>-14.52481683408551</v>
+        <v>-13.76791898940346</v>
       </c>
       <c r="F74">
-        <v>-2.262780141878276</v>
+        <v>-3.045685913244742</v>
       </c>
       <c r="G74">
-        <v>-4.470511872540639</v>
+        <v>-0.1919035423729951</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.157895948275252</v>
       </c>
       <c r="E75">
-        <v>-13.62450860235713</v>
+        <v>-13.98098703678981</v>
       </c>
       <c r="F75">
-        <v>-2.242092494360762</v>
+        <v>-3.585874237019134</v>
       </c>
       <c r="G75">
-        <v>-4.397233493357271</v>
+        <v>-0.3907665686226852</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.082260176937765</v>
       </c>
       <c r="E76">
-        <v>-14.10733603171375</v>
+        <v>-13.47473549556116</v>
       </c>
       <c r="F76">
-        <v>-2.955487471856113</v>
+        <v>-3.303046411416104</v>
       </c>
       <c r="G76">
-        <v>-4.793729885154237</v>
+        <v>-0.357920790921889</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.986019012486984</v>
       </c>
       <c r="E77">
-        <v>-14.30213825569351</v>
+        <v>-13.94036863003299</v>
       </c>
       <c r="F77">
-        <v>-2.071265740188045</v>
+        <v>-3.366160552202801</v>
       </c>
       <c r="G77">
-        <v>-3.948185423685786</v>
+        <v>0.3661170065315585</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.868633643870274</v>
       </c>
       <c r="E78">
-        <v>-14.9902256951458</v>
+        <v>-13.53732439022633</v>
       </c>
       <c r="F78">
-        <v>-2.838525308050434</v>
+        <v>-3.954068636950264</v>
       </c>
       <c r="G78">
-        <v>-4.074495857748438</v>
+        <v>0.3901489104927564</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.73141128202446</v>
       </c>
       <c r="E79">
-        <v>-14.83857533683101</v>
+        <v>-13.88705385625617</v>
       </c>
       <c r="F79">
-        <v>-2.880815120698154</v>
+        <v>-3.494603059843878</v>
       </c>
       <c r="G79">
-        <v>-3.598418749325157</v>
+        <v>0.1926669681317652</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.572929305675872</v>
       </c>
       <c r="E80">
-        <v>-16.56673487551482</v>
+        <v>-14.24982440584597</v>
       </c>
       <c r="F80">
-        <v>-2.932014853130386</v>
+        <v>-3.876939348075601</v>
       </c>
       <c r="G80">
-        <v>-3.147550990673666</v>
+        <v>-0.1044958134625223</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.400515707822274</v>
       </c>
       <c r="E81">
-        <v>-15.92970286287864</v>
+        <v>-14.69758211877573</v>
       </c>
       <c r="F81">
-        <v>-2.811136996611673</v>
+        <v>-4.04399703056558</v>
       </c>
       <c r="G81">
-        <v>-2.892201894450649</v>
+        <v>0.2724669873037339</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.221608631980637</v>
       </c>
       <c r="E82">
-        <v>-16.95093184232941</v>
+        <v>-15.07354326753319</v>
       </c>
       <c r="F82">
-        <v>-3.165709722971168</v>
+        <v>-4.235957922285921</v>
       </c>
       <c r="G82">
-        <v>-4.052422012230576</v>
+        <v>0.6587344817927179</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.041801217096532</v>
       </c>
       <c r="E83">
-        <v>-18.03512350546457</v>
+        <v>-15.85069632384643</v>
       </c>
       <c r="F83">
-        <v>-3.230852535527322</v>
+        <v>-4.67699895161924</v>
       </c>
       <c r="G83">
-        <v>-3.188307324485535</v>
+        <v>0.8329964617603475</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.87624388576609</v>
       </c>
       <c r="E84">
-        <v>-17.45721660924865</v>
+        <v>-17.03978149220146</v>
       </c>
       <c r="F84">
-        <v>-3.584519856315556</v>
+        <v>-4.5046861063259</v>
       </c>
       <c r="G84">
-        <v>-3.044888681117318</v>
+        <v>0.2042560633717171</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.736665814715816</v>
       </c>
       <c r="E85">
-        <v>-17.85912702236364</v>
+        <v>-17.26800460771211</v>
       </c>
       <c r="F85">
-        <v>-3.480495962974203</v>
+        <v>-4.546444107101023</v>
       </c>
       <c r="G85">
-        <v>-3.278291858307437</v>
+        <v>0.4990691748340026</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.632907810202958</v>
       </c>
       <c r="E86">
-        <v>-19.79878469455301</v>
+        <v>-18.09666579087588</v>
       </c>
       <c r="F86">
-        <v>-3.854126109802503</v>
+        <v>-4.737490481208673</v>
       </c>
       <c r="G86">
-        <v>-1.995254482727768</v>
+        <v>0.5101987790259186</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.582074236434188</v>
       </c>
       <c r="E87">
-        <v>-21.57449019648346</v>
+        <v>-19.41613687556259</v>
       </c>
       <c r="F87">
-        <v>-3.676968971937593</v>
+        <v>-5.248740618133667</v>
       </c>
       <c r="G87">
-        <v>-3.028414882747394</v>
+        <v>0.8664975363535131</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.591989163218814</v>
       </c>
       <c r="E88">
-        <v>-22.93661476147615</v>
+        <v>-20.4173016911031</v>
       </c>
       <c r="F88">
-        <v>-4.080349105670035</v>
+        <v>-5.354287050761366</v>
       </c>
       <c r="G88">
-        <v>-2.838483213743902</v>
+        <v>0.696603332086816</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.670269547372093</v>
       </c>
       <c r="E89">
-        <v>-23.58109763522907</v>
+        <v>-21.96934845676888</v>
       </c>
       <c r="F89">
-        <v>-4.56501361916958</v>
+        <v>-5.44563195263547</v>
       </c>
       <c r="G89">
-        <v>-2.010942446975768</v>
+        <v>0.436001417746479</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.827316087233319</v>
       </c>
       <c r="E90">
-        <v>-25.69022709552807</v>
+        <v>-23.64109077281621</v>
       </c>
       <c r="F90">
-        <v>-4.105024513864626</v>
+        <v>-5.860706977360636</v>
       </c>
       <c r="G90">
-        <v>-2.793090197538215</v>
+        <v>0.510138731900323</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.060413513109372</v>
       </c>
       <c r="E91">
-        <v>-26.309637032513</v>
+        <v>-25.18303692854001</v>
       </c>
       <c r="F91">
-        <v>-3.910965367512994</v>
+        <v>-6.136347887376976</v>
       </c>
       <c r="G91">
-        <v>-2.461828480839397</v>
+        <v>0.3797581470201254</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.37203936298146</v>
       </c>
       <c r="E92">
-        <v>-28.90105608130205</v>
+        <v>-27.31411611069073</v>
       </c>
       <c r="F92">
-        <v>-4.397506961547283</v>
+        <v>-6.394178069865725</v>
       </c>
       <c r="G92">
-        <v>-2.755706945738064</v>
+        <v>0.1413815013839358</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.764265038692153</v>
       </c>
       <c r="E93">
-        <v>-31.38227174419244</v>
+        <v>-28.6122957575207</v>
       </c>
       <c r="F93">
-        <v>-4.955095142617479</v>
+        <v>-6.602629271473596</v>
       </c>
       <c r="G93">
-        <v>-3.419212019101959</v>
+        <v>0.03062849433972799</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.225042027089965</v>
       </c>
       <c r="E94">
-        <v>-33.12092229468277</v>
+        <v>-31.09509587053151</v>
       </c>
       <c r="F94">
-        <v>-4.856038140223311</v>
+        <v>-6.836655488275498</v>
       </c>
       <c r="G94">
-        <v>-2.843532393783115</v>
+        <v>-0.2930594523002705</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.75236717088533</v>
       </c>
       <c r="E95">
-        <v>-34.56892073363328</v>
+        <v>-33.31058076643673</v>
       </c>
       <c r="F95">
-        <v>-5.079396641611961</v>
+        <v>-7.092849645143718</v>
       </c>
       <c r="G95">
-        <v>-4.100308289520775</v>
+        <v>-0.6861018290031935</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.33930146509287</v>
       </c>
       <c r="E96">
-        <v>-37.30640199489957</v>
+        <v>-34.71863777207636</v>
       </c>
       <c r="F96">
-        <v>-5.624465706123647</v>
+        <v>-7.510569646986021</v>
       </c>
       <c r="G96">
-        <v>-3.675031049351376</v>
+        <v>-1.120493178540169</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.959881023104335</v>
       </c>
       <c r="E97">
-        <v>-38.94566619838674</v>
+        <v>-38.71124233836812</v>
       </c>
       <c r="F97">
-        <v>-5.877524492372271</v>
+        <v>-7.535862188895699</v>
       </c>
       <c r="G97">
-        <v>-3.487477768670389</v>
+        <v>-1.249557948146445</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.612987847928959</v>
       </c>
       <c r="E98">
-        <v>-41.47905034872831</v>
+        <v>-40.02895661466442</v>
       </c>
       <c r="F98">
-        <v>-6.045912532911146</v>
+        <v>-7.85420129668934</v>
       </c>
       <c r="G98">
-        <v>-4.3534225883738</v>
+        <v>-1.466878938655306</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.264867439800806</v>
       </c>
       <c r="E99">
-        <v>-45.86680597670389</v>
+        <v>-42.61412092719828</v>
       </c>
       <c r="F99">
-        <v>-5.910538246843442</v>
+        <v>-8.240062288219976</v>
       </c>
       <c r="G99">
-        <v>-5.072638340567461</v>
+        <v>-1.897155754716687</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.914288403104341</v>
       </c>
       <c r="E100">
-        <v>-46.32484704087393</v>
+        <v>-44.89172332828329</v>
       </c>
       <c r="F100">
-        <v>-6.072000307527511</v>
+        <v>-8.381144025692969</v>
       </c>
       <c r="G100">
-        <v>-5.564839407585457</v>
+        <v>-2.278381901400231</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.514960555718575</v>
       </c>
       <c r="E101">
-        <v>-48.90122419654729</v>
+        <v>-47.71299043651384</v>
       </c>
       <c r="F101">
-        <v>-5.703061205301264</v>
+        <v>-8.475969727393636</v>
       </c>
       <c r="G101">
-        <v>-5.53391513790372</v>
+        <v>-2.807976663196743</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.107195035962924</v>
       </c>
       <c r="E102">
-        <v>-51.69505726737168</v>
+        <v>-50.19173078545464</v>
       </c>
       <c r="F102">
-        <v>-6.433235592907722</v>
+        <v>-8.79389258056737</v>
       </c>
       <c r="G102">
-        <v>-6.00698727930263</v>
+        <v>-3.081360783055171</v>
       </c>
     </row>
   </sheetData>
